--- a/Analysis/Prompt_Ablation/prompt_ablation_friedman_tests.xlsx
+++ b/Analysis/Prompt_Ablation/prompt_ablation_friedman_tests.xlsx
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2.772027972027817</v>
+        <v>1.907647907647787</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2500701036036889</v>
+        <v>0.3852649676223279</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2.291828793774092</v>
+        <v>2.758754863813109</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3179330678270239</v>
+        <v>0.2517352266048014</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
@@ -637,10 +637,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.01348314606721952</v>
+        <v>0.09438202247213084</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9932811003897493</v>
+        <v>0.9539051735812136</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
@@ -660,7 +660,7 @@
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>0.9932811003897493</v>
+        <v>1</v>
       </c>
       <c r="S4" t="b">
         <v>0</v>
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>13.04859335038335</v>
+        <v>21.92741935483857</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001467350808429939</v>
+        <v>1.731894312100037e-05</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
@@ -711,7 +711,7 @@
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>0.03521641940231854</v>
+        <v>0.0004156546349040089</v>
       </c>
       <c r="S5" t="b">
         <v>1</v>
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>11.33913043478107</v>
+        <v>10.83928571428633</v>
       </c>
       <c r="F6" t="n">
-        <v>0.003449364673897372</v>
+        <v>0.0044287280540101</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
@@ -762,7 +762,7 @@
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>0.07588602282574219</v>
+        <v>0.0930032891342121</v>
       </c>
       <c r="S6" t="b">
         <v>0</v>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.438547486033578</v>
+        <v>0.4336283185840386</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8031018445388534</v>
+        <v>0.8050795719610732</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
@@ -892,10 +892,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2.351297405189388</v>
+        <v>1.76518218623498</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3086187129783954</v>
+        <v>0.413709561709252</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.2063157894736689</v>
+        <v>0.02935010482211944</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9019845436252056</v>
+        <v>0.9854321013677525</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
@@ -966,7 +966,7 @@
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0.9854321013677525</v>
       </c>
       <c r="S10" t="b">
         <v>0</v>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.00264550264539</v>
+        <v>12.57181208053679</v>
       </c>
       <c r="F11" t="n">
-        <v>0.006729040262777443</v>
+        <v>0.001862368823980613</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
@@ -1017,10 +1017,10 @@
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>0.1413098455183263</v>
+        <v>0.04283448295155409</v>
       </c>
       <c r="S11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.233628318584213</v>
+        <v>1.841549295774702</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3273209276362922</v>
+        <v>0.3982104486919231</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.5952380952378787</v>
+        <v>0.5516074450082356</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7425841750805919</v>
+        <v>0.7589618832806699</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>0.8807688599048051</v>
+        <v>0.9233225810589356</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
@@ -1160,7 +1160,7 @@
         <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>7686.5</v>
+        <v>7635.5</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.01303287108371854</v>
+        <v>0.008376623376623376</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.0126758711374096</v>
+        <v>-0.004023668639053254</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>0.1715770268549506</v>
+        <v>0.2341762350536877</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -1233,7 +1233,7 @@
         <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>3791</v>
+        <v>3808.5</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.1362497151970836</v>
+        <v>0.1190145732130465</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0821301775147929</v>
+        <v>0.07229454306377384</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>0.008282243600190314</v>
+        <v>0.01286441172364076</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -1306,7 +1306,7 @@
         <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>1576.5</v>
+        <v>1692.5</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1319,18 +1319,18 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.3085526315789474</v>
+        <v>0.2878182200715338</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>small</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="P16" t="n">
-        <v>0.08118343195266273</v>
+        <v>0.07784352399737016</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="R16" t="n">
-        <v>0.1656448720038063</v>
+        <v>0.2572882344728152</v>
       </c>
       <c r="S16" t="b">
         <v>0</v>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>0.6509169543061128</v>
+        <v>0.7214344992646248</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -1379,7 +1379,7 @@
         <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>3010.5</v>
+        <v>926</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.04851453855878635</v>
+        <v>0.05171530977982591</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.02082840236686391</v>
+        <v>0.01233399079552926</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>0.03451250539565668</v>
+        <v>0.09762112338522023</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -1452,7 +1452,7 @@
         <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>164.5</v>
+        <v>189.5</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.4135472370766489</v>
+        <v>0.3244206773618538</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>33</v>
       </c>
       <c r="P18" t="n">
-        <v>0.03326758711374096</v>
+        <v>0.02274819197896121</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>0.6212250971218203</v>
+        <v>1</v>
       </c>
       <c r="S18" t="b">
         <v>0</v>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>0.3903891403830421</v>
+        <v>0.2602755536860685</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -1525,7 +1525,7 @@
         <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>154</v>
+        <v>154.5</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>-0.1851851851851852</v>
+        <v>-0.2389162561576355</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.01186061801446417</v>
+        <v>-0.01627876397107166</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>0.07254039512328656</v>
+        <v>0.08094797166424243</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -1598,7 +1598,7 @@
         <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>6039</v>
+        <v>5138</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.1592064044552732</v>
+        <v>0.1608688551363711</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="P20" t="n">
-        <v>0.04131492439184747</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>0.001743496912838276</v>
+        <v>0.00204193628054538</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -1671,7 +1671,7 @@
         <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>2149</v>
+        <v>2251.5</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.3327123117528334</v>
+        <v>0.324887556221889</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1136620644312952</v>
+        <v>0.1091387245233399</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>0.04010042899528035</v>
+        <v>0.04492259817199836</v>
       </c>
       <c r="S21" t="b">
         <v>1</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>0.3306491040301512</v>
+        <v>0.3837245232320642</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -1744,7 +1744,7 @@
         <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>1770.5</v>
+        <v>1795</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.1158551810237203</v>
+        <v>0.1036204744069913</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>89</v>
       </c>
       <c r="P22" t="n">
-        <v>0.05067718606180144</v>
+        <v>0.0482577251808021</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>0.0963371145999003</v>
+        <v>0.1451341377813551</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -1817,7 +1817,7 @@
         <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>7725.5</v>
+        <v>7456.5</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>-0.1394597605123921</v>
+        <v>-0.1237955346650999</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1079026955950033</v>
+        <v>-0.08907297830374754</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
-        <v>0.2693573467437352</v>
+        <v>0.2534826383210801</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -1890,7 +1890,7 @@
         <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>3786.5</v>
+        <v>3770.5</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.1106283029947152</v>
+        <v>0.1143863769817968</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>130</v>
       </c>
       <c r="P24" t="n">
-        <v>0.06574621959237344</v>
+        <v>0.06966469428007889</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>0.1656555999789144</v>
+        <v>0.1717908742652029</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -1963,7 +1963,7 @@
         <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>3492</v>
+        <v>3557.5</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.140748031496063</v>
+        <v>0.138202519379845</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P25" t="n">
-        <v>0.05593688362919132</v>
+        <v>0.05577909270216962</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
